--- a/outputs/D_mixed.xlsx
+++ b/outputs/D_mixed.xlsx
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validation Report'!$A$1:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Audit'!$A$1:$L$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Provenance'!$A$1:$E$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cell Evidence'!$A$1:$M$313</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Verification'!$A$1:$B$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Constraints'!$A$1:$H$2</definedName>
@@ -2371,7 +2371,7 @@
         <v>0.98</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>0.227</v>
+        <v>0.141</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>0.96</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>3.206</v>
+        <v>3.091</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3040,95 +3040,131 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>4.711</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
+        <v>4.075</v>
+      </c>
+    </row>
+    <row r="4" ht="119" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Yellow cells</t>
+          <t>Text encoding</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Review required. See Validation Report for the reason and source row.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
+          <t>All XLSX string fields use a reversible encoding: a literal backslash is doubled; XML-forbidden code points use a backslash followed by u and four hexadecimal digits. An underscore starting an OOXML escape-like sequence uses the same Unicode encoding. Decode left to right, treating each doubled backslash as one literal backslash. The full audit JSON and saved workspace retain the original strings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="68" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Source row</t>
+          <t>Long text</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Data row within the extracted source table, excluding detected headers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
+          <t>Values exceeding Excel's 32767-character cell limit show an explicit preview. The Long Text sheet preserves the complete encoded value in numbered chunks. Join its chunks in order before decoding the text encoding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="68" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Confidence</t>
+          <t>Small numbers</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Extraction heuristic / OCR score, not a calibrated probability of correctness.</t>
+          <t>Numbers below Excel's normal floating-point range remain exact text. Numbers needing more than 12 decimal places use General formatting; percentages needing more than 12 display decimals remain text, avoiding a false zero.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Dates</t>
+          <t>Yellow cells</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>ISO and unambiguous day-first dates are typed. Ambiguous dates stay text.</t>
+          <t>Review required. See Validation Report for the reason and source row.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Source row</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Source strings are stored as text. No source formulas are executed.</t>
+          <t>Data row within the extracted source table, excluding detected headers.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Cell evidence</t>
+          <t>Confidence</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Ctrl+click a linked data cell for its source bounding box and original readings.</t>
+          <t>Extraction heuristic / OCR score, not a calibrated probability of correctness.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>ISO and unambiguous day-first dates are typed. Ambiguous dates stay text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Source strings are stored as text. No source formulas are executed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Cell evidence</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Ctrl+click a linked data cell for its source bounding box and original readings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
           <t>Repair proposals</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Arithmetic-derived suggestions only. Source documents may contain errors. Never applied automatically.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B10"/>
+  <autoFilter ref="A1:B13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3288,13 +3324,13 @@
         <v>34.8</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>120</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -3380,13 +3416,13 @@
         <v>120</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>209.76</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -3472,13 +3508,13 @@
         <v>209.76</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>300</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
@@ -3564,13 +3600,13 @@
         <v>300</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>374.88</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
@@ -3656,13 +3692,13 @@
         <v>374.88</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>554.88</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
@@ -3748,13 +3784,13 @@
         <v>554.88</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>610.08</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
@@ -3840,13 +3876,13 @@
         <v>610.08</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>680.16</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
@@ -3932,13 +3968,13 @@
         <v>680.16</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>759.84</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
@@ -4024,13 +4060,13 @@
         <v>759.84</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>829.92</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
@@ -4116,13 +4152,13 @@
         <v>829.92</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>894.96</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
@@ -4208,13 +4244,13 @@
         <v>894.96</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>984.96</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
@@ -4300,13 +4336,13 @@
         <v>984.96</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>93.84</v>
+        <v>92.16</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>1085.04</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
@@ -10827,7 +10863,7 @@
         <v>34.8</v>
       </c>
       <c r="F170" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G170" s="7" t="n">
         <v>120</v>
@@ -10878,7 +10914,7 @@
         <v>120</v>
       </c>
       <c r="F171" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G171" s="7" t="n">
         <v>209.76</v>
@@ -10929,7 +10965,7 @@
         <v>209.76</v>
       </c>
       <c r="F172" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G172" s="7" t="n">
         <v>300</v>
@@ -10980,7 +11016,7 @@
         <v>300</v>
       </c>
       <c r="F173" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G173" s="7" t="n">
         <v>374.88</v>
@@ -11031,7 +11067,7 @@
         <v>374.88</v>
       </c>
       <c r="F174" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G174" s="7" t="n">
         <v>554.88</v>
@@ -11082,7 +11118,7 @@
         <v>554.88</v>
       </c>
       <c r="F175" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G175" s="7" t="n">
         <v>610.08</v>
@@ -11133,7 +11169,7 @@
         <v>610.08</v>
       </c>
       <c r="F176" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G176" s="7" t="n">
         <v>680.16</v>
@@ -11184,7 +11220,7 @@
         <v>680.16</v>
       </c>
       <c r="F177" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G177" s="7" t="n">
         <v>759.84</v>
@@ -11235,7 +11271,7 @@
         <v>759.84</v>
       </c>
       <c r="F178" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G178" s="7" t="n">
         <v>829.92</v>
@@ -11286,7 +11322,7 @@
         <v>829.92</v>
       </c>
       <c r="F179" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G179" s="7" t="n">
         <v>894.96</v>
@@ -11337,7 +11373,7 @@
         <v>894.96</v>
       </c>
       <c r="F180" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G180" s="7" t="n">
         <v>984.96</v>
@@ -11388,7 +11424,7 @@
         <v>984.96</v>
       </c>
       <c r="F181" s="7" t="n">
-        <v>116.88</v>
+        <v>119.04</v>
       </c>
       <c r="G181" s="7" t="n">
         <v>1085.04</v>
@@ -18203,7 +18239,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>60c3d03c01d61b06410496d0ed22d37be335e1edd26de55d4af1140232305b30</t>
+          <t>c590a9675dba6f0e6f5cf71c5c5f52d695da7b22b108a02b7a3ce773261a4389</t>
         </is>
       </c>
     </row>

--- a/outputs/D_mixed.xlsx
+++ b/outputs/D_mixed.xlsx
@@ -10,25 +10,27 @@
     <sheet name="Data 1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Validation Report" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Page Audit" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Provenance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Read me" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cell Evidence" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Verification" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Constraints" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Repair Proposals" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Correction History" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Join Receipt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Provenance" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Read me" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cell Evidence" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Verification" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Constraints" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Repair Proposals" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Correction History" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data 1'!$A$1:$L$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validation Report'!$A$1:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Audit'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Provenance'!$A$1:$E$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cell Evidence'!$A$1:$M$313</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Verification'!$A$1:$B$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Constraints'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Correction History'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Join Receipt'!$A$1:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Provenance'!$A$1:$E$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Read me'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cell Evidence'!$A$1:$M$313</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Verification'!$A$1:$B$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Constraints'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Correction History'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2082,6 +2084,79 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Excel row</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Observed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Supporting equations</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Caution</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
@@ -2371,7 +2446,7 @@
         <v>0.98</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>0.141</v>
+        <v>0.529</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
@@ -2413,7 +2488,7 @@
         <v>0.96</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>3.091</v>
+        <v>6.782</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -2444,6 +2519,133 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data sheet</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Source pages</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Page joins</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Repeated headers removed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Split rows recovered</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>PDF page</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Source rows on page</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Output rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2996,7 +3198,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3040,7 +3242,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>4.075</v>
+        <v>9.821</v>
       </c>
     </row>
     <row r="4" ht="119" customHeight="1">
@@ -3169,7 +3371,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18194,7 +18396,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18239,7 +18441,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>c590a9675dba6f0e6f5cf71c5c5f52d695da7b22b108a02b7a3ce773261a4389</t>
+          <t>33b0712165514ce4428b278ec50d59671af69fa529c0a77d2139f7967ab01cab</t>
         </is>
       </c>
     </row>
@@ -18341,7 +18543,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18438,77 +18640,4 @@
   <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Excel row</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Supporting equations</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Caution</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/outputs/D_mixed.xlsx
+++ b/outputs/D_mixed.xlsx
@@ -22,12 +22,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data 1'!$A$1:$L$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validation Report'!$A$1:$H$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Audit'!$A$1:$L$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Audit'!$A$1:$L$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Join Receipt'!$A$1:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Provenance'!$A$1:$E$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Read me'!$A$1:$B$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cell Evidence'!$A$1:$M$313</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Verification'!$A$1:$B$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cell Evidence'!$A$1:$O$313</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Verification'!$A$1:$B$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Constraints'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Correction History'!$A$1:$I$1</definedName>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>OCR tesseract; deskew correction 0.00 degrees; values require source review.</t>
+          <t>OCR rapidocr; deskew correction 0.00 degrees; values require source review.</t>
         </is>
       </c>
       <c r="H2" s="7" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>OCR tesseract; deskew correction 0.00 degrees; values require source review.</t>
+          <t>OCR rapidocr; deskew correction 0.00 degrees; values require source review.</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
@@ -2349,15 +2349,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
@@ -2446,7 +2446,7 @@
         <v>0.98</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>0.529</v>
+        <v>0.309</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999354511499405</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>6.782</v>
+        <v>4.353</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="G3" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>1</v>
@@ -2512,8 +2512,50 @@
       </c>
       <c r="L3" s="7" t="inlineStr"/>
     </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>rapidocr</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>0.9999354511499405</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>5.975</v>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>independent-language-aware-cross-check</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>144</v>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>842.999</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2658,7 +2700,7 @@
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2957,7 +2999,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
     </row>
@@ -2978,7 +3020,7 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
     </row>
@@ -2999,7 +3041,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3062,7 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3083,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3104,7 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3125,7 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3146,7 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3167,7 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3188,7 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3209,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3230,7 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3284,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>9.821</v>
+        <v>12.531</v>
       </c>
     </row>
     <row r="4" ht="119" customHeight="1">
@@ -3377,7 +3419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M313"/>
+  <dimension ref="A1:O313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3388,11 +3430,13 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3461,6 +3505,16 @@
           <t>Role</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Location status</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Location reason</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="17" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
@@ -3506,6 +3560,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O2" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="17" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
@@ -3536,11 +3600,11 @@
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J3" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9998472332954407</v>
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
@@ -3553,6 +3617,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -3598,6 +3672,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O4" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -3628,11 +3712,11 @@
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J5" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9998795390129089</v>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
@@ -3645,6 +3729,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
@@ -3690,6 +3784,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -3720,11 +3824,11 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J7" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9995063344637553</v>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
@@ -3737,6 +3841,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -3782,6 +3896,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -3812,11 +3936,11 @@
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J9" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9998641411463419</v>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
@@ -3829,6 +3953,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
@@ -3874,6 +4008,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
@@ -3904,11 +4048,11 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J11" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9997081594033674</v>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
@@ -3921,6 +4065,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
@@ -3966,6 +4120,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
@@ -3996,11 +4160,11 @@
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J13" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9999770224094391</v>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
@@ -4013,6 +4177,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
@@ -4058,6 +4232,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
@@ -4088,11 +4272,11 @@
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J15" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999109655618668</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
@@ -4105,6 +4289,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
@@ -4150,6 +4344,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
@@ -4180,11 +4384,11 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J17" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999066392580668</v>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
@@ -4197,6 +4401,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
@@ -4242,6 +4456,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
@@ -4272,11 +4496,11 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J19" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999334812164307</v>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
@@ -4289,6 +4513,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
@@ -4334,6 +4568,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
@@ -4364,11 +4608,11 @@
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J21" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9998739361763</v>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
@@ -4381,6 +4625,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
@@ -4426,6 +4680,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
@@ -4456,11 +4720,11 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J23" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999604026476542</v>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
@@ -4473,6 +4737,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
@@ -4518,6 +4792,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N24" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
@@ -4548,11 +4832,11 @@
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J25" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999742905298868</v>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
@@ -4565,6 +4849,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
@@ -4610,6 +4904,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
@@ -4655,6 +4959,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
@@ -4700,6 +5014,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
@@ -4745,6 +5069,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
@@ -4790,6 +5124,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
@@ -4835,6 +5179,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O31" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
@@ -4880,6 +5234,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N32" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O32" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
@@ -4925,6 +5289,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N33" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O33" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
@@ -4970,6 +5344,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N34" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O34" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
@@ -5015,6 +5399,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N35" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O35" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
@@ -5060,6 +5454,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N36" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O36" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
@@ -5105,6 +5509,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O37" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
@@ -5150,6 +5564,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N38" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O38" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
@@ -5195,6 +5619,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N39" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O39" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
@@ -5240,6 +5674,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N40" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O40" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
@@ -5285,6 +5729,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N41" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O41" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
@@ -5330,6 +5784,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N42" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O42" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
@@ -5375,6 +5839,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N43" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O43" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="17" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
@@ -5420,6 +5894,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N44" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O44" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="17" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
@@ -5465,6 +5949,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O45" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="17" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
@@ -5510,6 +6004,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N46" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O46" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="17" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
@@ -5555,6 +6059,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O47" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
@@ -5600,6 +6114,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N48" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O48" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="17" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
@@ -5645,6 +6169,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N49" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O49" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="17" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
@@ -5690,6 +6224,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N50" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O50" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="17" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
@@ -5735,6 +6279,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N51" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O51" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="17" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
@@ -5780,6 +6334,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N52" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O52" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="17" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
@@ -5825,6 +6389,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N53" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O53" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="17" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
@@ -5870,6 +6444,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N54" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O54" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="17" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
@@ -5915,6 +6499,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N55" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O55" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="17" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
@@ -5960,6 +6554,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N56" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O56" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="17" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
@@ -6005,6 +6609,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N57" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O57" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="17" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
@@ -6050,6 +6664,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N58" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O58" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="17" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
@@ -6095,6 +6719,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N59" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O59" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="17" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
@@ -6140,6 +6774,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N60" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O60" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="17" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
@@ -6185,6 +6829,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N61" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O61" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="17" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
@@ -6230,6 +6884,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N62" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O62" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="17" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
@@ -6275,6 +6939,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N63" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O63" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="17" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
@@ -6320,6 +6994,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N64" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O64" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="17" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
@@ -6365,6 +7049,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N65" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O65" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="17" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
@@ -6410,6 +7104,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N66" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O66" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="17" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
@@ -6455,6 +7159,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N67" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O67" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="17" customHeight="1">
       <c r="A68" s="7" t="inlineStr">
@@ -6500,6 +7214,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N68" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O68" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="17" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
@@ -6545,6 +7269,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N69" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O69" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="17" customHeight="1">
       <c r="A70" s="7" t="inlineStr">
@@ -6590,6 +7324,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N70" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O70" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="17" customHeight="1">
       <c r="A71" s="7" t="inlineStr">
@@ -6635,6 +7379,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N71" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O71" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="17" customHeight="1">
       <c r="A72" s="7" t="inlineStr">
@@ -6680,6 +7434,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N72" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O72" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="17" customHeight="1">
       <c r="A73" s="7" t="inlineStr">
@@ -6725,6 +7489,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N73" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O73" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="17" customHeight="1">
       <c r="A74" s="7" t="inlineStr">
@@ -6770,6 +7544,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N74" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O74" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="17" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
@@ -6815,6 +7599,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N75" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O75" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="17" customHeight="1">
       <c r="A76" s="7" t="inlineStr">
@@ -6860,6 +7654,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N76" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O76" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="17" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
@@ -6905,6 +7709,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N77" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O77" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="17" customHeight="1">
       <c r="A78" s="7" t="inlineStr">
@@ -6950,6 +7764,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N78" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O78" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="17" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
@@ -6995,6 +7819,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N79" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O79" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="17" customHeight="1">
       <c r="A80" s="7" t="inlineStr">
@@ -7040,6 +7874,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N80" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O80" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="17" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
@@ -7085,6 +7929,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N81" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O81" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="17" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
@@ -7130,6 +7984,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N82" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O82" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="17" customHeight="1">
       <c r="A83" s="7" t="inlineStr">
@@ -7175,6 +8039,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N83" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O83" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="17" customHeight="1">
       <c r="A84" s="7" t="inlineStr">
@@ -7220,6 +8094,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N84" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O84" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="17" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
@@ -7265,6 +8149,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N85" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O85" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="17" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
@@ -7310,6 +8204,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N86" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O86" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="17" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
@@ -7355,6 +8259,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N87" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O87" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="17" customHeight="1">
       <c r="A88" s="7" t="inlineStr">
@@ -7400,6 +8314,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N88" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O88" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="17" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
@@ -7445,6 +8369,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N89" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O89" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="17" customHeight="1">
       <c r="A90" s="7" t="inlineStr">
@@ -7490,6 +8424,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N90" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O90" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="17" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
@@ -7535,6 +8479,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N91" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O91" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="17" customHeight="1">
       <c r="A92" s="7" t="inlineStr">
@@ -7580,6 +8534,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N92" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O92" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="17" customHeight="1">
       <c r="A93" s="7" t="inlineStr">
@@ -7625,6 +8589,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N93" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O93" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="17" customHeight="1">
       <c r="A94" s="7" t="inlineStr">
@@ -7670,6 +8644,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N94" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O94" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="17" customHeight="1">
       <c r="A95" s="7" t="inlineStr">
@@ -7715,6 +8699,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N95" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O95" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="17" customHeight="1">
       <c r="A96" s="7" t="inlineStr">
@@ -7760,6 +8754,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N96" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O96" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="17" customHeight="1">
       <c r="A97" s="7" t="inlineStr">
@@ -7805,6 +8809,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N97" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O97" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="17" customHeight="1">
       <c r="A98" s="7" t="inlineStr">
@@ -7850,6 +8864,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N98" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O98" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="17" customHeight="1">
       <c r="A99" s="7" t="inlineStr">
@@ -7895,6 +8919,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N99" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O99" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="17" customHeight="1">
       <c r="A100" s="7" t="inlineStr">
@@ -7940,6 +8974,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N100" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O100" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="17" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
@@ -7985,6 +9029,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N101" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O101" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="17" customHeight="1">
       <c r="A102" s="7" t="inlineStr">
@@ -8030,6 +9084,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N102" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O102" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="17" customHeight="1">
       <c r="A103" s="7" t="inlineStr">
@@ -8075,6 +9139,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N103" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O103" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="17" customHeight="1">
       <c r="A104" s="7" t="inlineStr">
@@ -8120,6 +9194,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N104" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O104" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="17" customHeight="1">
       <c r="A105" s="7" t="inlineStr">
@@ -8165,6 +9249,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N105" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O105" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="17" customHeight="1">
       <c r="A106" s="7" t="inlineStr">
@@ -8210,6 +9304,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N106" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O106" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="17" customHeight="1">
       <c r="A107" s="7" t="inlineStr">
@@ -8255,6 +9359,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N107" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O107" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="17" customHeight="1">
       <c r="A108" s="7" t="inlineStr">
@@ -8300,6 +9414,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N108" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O108" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="17" customHeight="1">
       <c r="A109" s="7" t="inlineStr">
@@ -8345,6 +9469,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N109" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O109" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="17" customHeight="1">
       <c r="A110" s="7" t="inlineStr">
@@ -8390,6 +9524,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N110" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O110" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="17" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
@@ -8435,6 +9579,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N111" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O111" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="17" customHeight="1">
       <c r="A112" s="7" t="inlineStr">
@@ -8480,6 +9634,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N112" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O112" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="17" customHeight="1">
       <c r="A113" s="7" t="inlineStr">
@@ -8525,6 +9689,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N113" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O113" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="17" customHeight="1">
       <c r="A114" s="7" t="inlineStr">
@@ -8570,6 +9744,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N114" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O114" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="17" customHeight="1">
       <c r="A115" s="7" t="inlineStr">
@@ -8615,6 +9799,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N115" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O115" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="17" customHeight="1">
       <c r="A116" s="7" t="inlineStr">
@@ -8660,6 +9854,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N116" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O116" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="17" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
@@ -8705,6 +9909,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N117" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O117" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="17" customHeight="1">
       <c r="A118" s="7" t="inlineStr">
@@ -8750,6 +9964,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N118" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O118" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="17" customHeight="1">
       <c r="A119" s="7" t="inlineStr">
@@ -8795,6 +10019,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N119" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O119" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="17" customHeight="1">
       <c r="A120" s="7" t="inlineStr">
@@ -8840,6 +10074,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N120" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O120" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="17" customHeight="1">
       <c r="A121" s="7" t="inlineStr">
@@ -8885,6 +10129,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N121" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O121" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="17" customHeight="1">
       <c r="A122" s="7" t="inlineStr">
@@ -8930,6 +10184,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N122" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O122" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="17" customHeight="1">
       <c r="A123" s="7" t="inlineStr">
@@ -8975,6 +10239,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N123" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O123" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="17" customHeight="1">
       <c r="A124" s="7" t="inlineStr">
@@ -9020,6 +10294,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N124" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O124" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="17" customHeight="1">
       <c r="A125" s="7" t="inlineStr">
@@ -9065,6 +10349,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N125" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O125" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="17" customHeight="1">
       <c r="A126" s="7" t="inlineStr">
@@ -9110,6 +10404,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N126" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O126" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="17" customHeight="1">
       <c r="A127" s="7" t="inlineStr">
@@ -9155,6 +10459,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N127" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O127" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="17" customHeight="1">
       <c r="A128" s="7" t="inlineStr">
@@ -9200,6 +10514,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N128" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O128" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="17" customHeight="1">
       <c r="A129" s="7" t="inlineStr">
@@ -9245,6 +10569,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N129" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O129" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="17" customHeight="1">
       <c r="A130" s="7" t="inlineStr">
@@ -9290,6 +10624,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N130" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O130" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="17" customHeight="1">
       <c r="A131" s="7" t="inlineStr">
@@ -9335,6 +10679,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N131" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O131" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="17" customHeight="1">
       <c r="A132" s="7" t="inlineStr">
@@ -9380,6 +10734,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N132" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O132" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="17" customHeight="1">
       <c r="A133" s="7" t="inlineStr">
@@ -9425,6 +10789,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N133" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O133" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="17" customHeight="1">
       <c r="A134" s="7" t="inlineStr">
@@ -9470,6 +10844,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N134" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O134" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="17" customHeight="1">
       <c r="A135" s="7" t="inlineStr">
@@ -9515,6 +10899,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N135" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O135" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="17" customHeight="1">
       <c r="A136" s="7" t="inlineStr">
@@ -9560,6 +10954,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N136" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O136" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="17" customHeight="1">
       <c r="A137" s="7" t="inlineStr">
@@ -9605,6 +11009,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N137" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O137" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="17" customHeight="1">
       <c r="A138" s="7" t="inlineStr">
@@ -9650,6 +11064,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N138" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O138" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="17" customHeight="1">
       <c r="A139" s="7" t="inlineStr">
@@ -9695,6 +11119,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N139" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O139" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="17" customHeight="1">
       <c r="A140" s="7" t="inlineStr">
@@ -9740,6 +11174,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N140" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O140" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="17" customHeight="1">
       <c r="A141" s="7" t="inlineStr">
@@ -9785,6 +11229,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N141" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O141" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="17" customHeight="1">
       <c r="A142" s="7" t="inlineStr">
@@ -9830,6 +11284,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N142" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O142" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="17" customHeight="1">
       <c r="A143" s="7" t="inlineStr">
@@ -9875,6 +11339,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N143" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O143" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="17" customHeight="1">
       <c r="A144" s="7" t="inlineStr">
@@ -9920,6 +11394,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N144" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O144" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="17" customHeight="1">
       <c r="A145" s="7" t="inlineStr">
@@ -9965,6 +11449,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N145" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O145" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="17" customHeight="1">
       <c r="A146" s="7" t="inlineStr">
@@ -10010,6 +11504,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N146" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O146" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="17" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
@@ -10055,6 +11559,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N147" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O147" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="17" customHeight="1">
       <c r="A148" s="7" t="inlineStr">
@@ -10100,6 +11614,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N148" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O148" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="17" customHeight="1">
       <c r="A149" s="7" t="inlineStr">
@@ -10145,6 +11669,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N149" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O149" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="17" customHeight="1">
       <c r="A150" s="7" t="inlineStr">
@@ -10190,6 +11724,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N150" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O150" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="17" customHeight="1">
       <c r="A151" s="7" t="inlineStr">
@@ -10235,6 +11779,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N151" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O151" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="17" customHeight="1">
       <c r="A152" s="7" t="inlineStr">
@@ -10280,6 +11834,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N152" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O152" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="17" customHeight="1">
       <c r="A153" s="7" t="inlineStr">
@@ -10325,6 +11889,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N153" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O153" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="17" customHeight="1">
       <c r="A154" s="7" t="inlineStr">
@@ -10370,6 +11944,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N154" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O154" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="17" customHeight="1">
       <c r="A155" s="7" t="inlineStr">
@@ -10415,6 +11999,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N155" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O155" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="17" customHeight="1">
       <c r="A156" s="7" t="inlineStr">
@@ -10460,6 +12054,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N156" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O156" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="17" customHeight="1">
       <c r="A157" s="7" t="inlineStr">
@@ -10505,6 +12109,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N157" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O157" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="17" customHeight="1">
       <c r="A158" s="7" t="inlineStr">
@@ -10550,6 +12164,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N158" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O158" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="17" customHeight="1">
       <c r="A159" s="7" t="inlineStr">
@@ -10595,6 +12219,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N159" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O159" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="17" customHeight="1">
       <c r="A160" s="7" t="inlineStr">
@@ -10640,6 +12274,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N160" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O160" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="17" customHeight="1">
       <c r="A161" s="7" t="inlineStr">
@@ -10685,6 +12329,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N161" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O161" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="17" customHeight="1">
       <c r="A162" s="7" t="inlineStr">
@@ -10730,6 +12384,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N162" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O162" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="17" customHeight="1">
       <c r="A163" s="7" t="inlineStr">
@@ -10775,6 +12439,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N163" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O163" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="17" customHeight="1">
       <c r="A164" s="7" t="inlineStr">
@@ -10820,6 +12494,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N164" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O164" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="17" customHeight="1">
       <c r="A165" s="7" t="inlineStr">
@@ -10865,6 +12549,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N165" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O165" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="17" customHeight="1">
       <c r="A166" s="7" t="inlineStr">
@@ -10910,6 +12604,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N166" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O166" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="17" customHeight="1">
       <c r="A167" s="7" t="inlineStr">
@@ -10955,6 +12659,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N167" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O167" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="17" customHeight="1">
       <c r="A168" s="7" t="inlineStr">
@@ -11000,6 +12714,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N168" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O168" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="17" customHeight="1">
       <c r="A169" s="7" t="inlineStr">
@@ -11045,6 +12769,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N169" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O169" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="17" customHeight="1">
       <c r="A170" s="7" t="inlineStr">
@@ -11075,11 +12809,11 @@
       </c>
       <c r="I170" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J170" s="7" t="n">
-        <v>0.9</v>
+        <v>0.9999687671661377</v>
       </c>
       <c r="K170" s="7" t="inlineStr">
         <is>
@@ -11094,6 +12828,16 @@
       <c r="M170" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N170" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O170" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -11126,11 +12870,11 @@
       </c>
       <c r="I171" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J171" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999916434288025</v>
       </c>
       <c r="K171" s="7" t="inlineStr">
         <is>
@@ -11145,6 +12889,16 @@
       <c r="M171" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N171" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O171" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -11177,11 +12931,11 @@
       </c>
       <c r="I172" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J172" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9386227503418922</v>
       </c>
       <c r="K172" s="7" t="inlineStr">
         <is>
@@ -11196,6 +12950,16 @@
       <c r="M172" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N172" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O172" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -11228,11 +12992,11 @@
       </c>
       <c r="I173" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J173" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999212423960367</v>
       </c>
       <c r="K173" s="7" t="inlineStr">
         <is>
@@ -11247,6 +13011,16 @@
       <c r="M173" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N173" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O173" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -11279,11 +13053,11 @@
       </c>
       <c r="I174" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J174" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9998136480649312</v>
       </c>
       <c r="K174" s="7" t="inlineStr">
         <is>
@@ -11298,6 +13072,16 @@
       <c r="M174" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N174" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O174" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -11330,11 +13114,11 @@
       </c>
       <c r="I175" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J175" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999961853027344</v>
       </c>
       <c r="K175" s="7" t="inlineStr">
         <is>
@@ -11349,6 +13133,16 @@
       <c r="M175" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N175" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O175" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -11381,11 +13175,11 @@
       </c>
       <c r="I176" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J176" s="7" t="n">
-        <v>0.96</v>
+        <v>0.999926221370697</v>
       </c>
       <c r="K176" s="7" t="inlineStr">
         <is>
@@ -11400,6 +13194,16 @@
       <c r="M176" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N176" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O176" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -11432,11 +13236,11 @@
       </c>
       <c r="I177" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J177" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999614953994751</v>
       </c>
       <c r="K177" s="7" t="inlineStr">
         <is>
@@ -11451,6 +13255,16 @@
       <c r="M177" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N177" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O177" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -11483,11 +13297,11 @@
       </c>
       <c r="I178" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J178" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999672770500183</v>
       </c>
       <c r="K178" s="7" t="inlineStr">
         <is>
@@ -11502,6 +13316,16 @@
       <c r="M178" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N178" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O178" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -11534,11 +13358,11 @@
       </c>
       <c r="I179" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J179" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999361932277679</v>
       </c>
       <c r="K179" s="7" t="inlineStr">
         <is>
@@ -11553,6 +13377,16 @@
       <c r="M179" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N179" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O179" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -11585,11 +13419,11 @@
       </c>
       <c r="I180" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J180" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999462842941285</v>
       </c>
       <c r="K180" s="7" t="inlineStr">
         <is>
@@ -11604,6 +13438,16 @@
       <c r="M180" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N180" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O180" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -11636,11 +13480,11 @@
       </c>
       <c r="I181" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J181" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9998781979084015</v>
       </c>
       <c r="K181" s="7" t="inlineStr">
         <is>
@@ -11655,6 +13499,16 @@
       <c r="M181" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N181" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O181" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -11687,11 +13541,11 @@
       </c>
       <c r="I182" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J182" s="7" t="n">
-        <v>0.89</v>
+        <v>0.9999647438526154</v>
       </c>
       <c r="K182" s="7" t="inlineStr">
         <is>
@@ -11706,6 +13560,16 @@
       <c r="M182" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N182" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O182" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -11738,11 +13602,11 @@
       </c>
       <c r="I183" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J183" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999909996986389</v>
       </c>
       <c r="K183" s="7" t="inlineStr">
         <is>
@@ -11757,6 +13621,16 @@
       <c r="M183" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N183" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O183" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -11789,11 +13663,11 @@
       </c>
       <c r="I184" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J184" s="7" t="n">
-        <v>0.92</v>
+        <v>0.9980887547135353</v>
       </c>
       <c r="K184" s="7" t="inlineStr">
         <is>
@@ -11808,6 +13682,16 @@
       <c r="M184" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N184" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O184" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -11840,11 +13724,11 @@
       </c>
       <c r="I185" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J185" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999114175637563</v>
       </c>
       <c r="K185" s="7" t="inlineStr">
         <is>
@@ -11859,6 +13743,16 @@
       <c r="M185" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N185" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O185" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -11891,11 +13785,11 @@
       </c>
       <c r="I186" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J186" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9996509424277714</v>
       </c>
       <c r="K186" s="7" t="inlineStr">
         <is>
@@ -11910,6 +13804,16 @@
       <c r="M186" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N186" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O186" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -11942,11 +13846,11 @@
       </c>
       <c r="I187" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J187" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999948740005493</v>
       </c>
       <c r="K187" s="7" t="inlineStr">
         <is>
@@ -11961,6 +13865,16 @@
       <c r="M187" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N187" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O187" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -11993,11 +13907,11 @@
       </c>
       <c r="I188" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J188" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999682664871216</v>
       </c>
       <c r="K188" s="7" t="inlineStr">
         <is>
@@ -12012,6 +13926,16 @@
       <c r="M188" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N188" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O188" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -12044,11 +13968,11 @@
       </c>
       <c r="I189" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J189" s="7" t="n">
-        <v>0.95</v>
+        <v>0.999960470199585</v>
       </c>
       <c r="K189" s="7" t="inlineStr">
         <is>
@@ -12063,6 +13987,16 @@
       <c r="M189" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N189" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O189" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -12095,11 +14029,11 @@
       </c>
       <c r="I190" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J190" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999549984931946</v>
       </c>
       <c r="K190" s="7" t="inlineStr">
         <is>
@@ -12114,6 +14048,16 @@
       <c r="M190" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N190" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O190" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -12146,11 +14090,11 @@
       </c>
       <c r="I191" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J191" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999276101589203</v>
       </c>
       <c r="K191" s="7" t="inlineStr">
         <is>
@@ -12165,6 +14109,16 @@
       <c r="M191" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N191" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O191" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -12197,11 +14151,11 @@
       </c>
       <c r="I192" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J192" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999284505844116</v>
       </c>
       <c r="K192" s="7" t="inlineStr">
         <is>
@@ -12216,6 +14170,16 @@
       <c r="M192" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N192" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O192" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -12248,11 +14212,11 @@
       </c>
       <c r="I193" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J193" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9998601973056793</v>
       </c>
       <c r="K193" s="7" t="inlineStr">
         <is>
@@ -12267,6 +14231,16 @@
       <c r="M193" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N193" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O193" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -12299,11 +14273,11 @@
       </c>
       <c r="I194" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J194" s="7" t="n">
-        <v>0.9</v>
+        <v>0.9999643564224243</v>
       </c>
       <c r="K194" s="7" t="inlineStr">
         <is>
@@ -12318,6 +14292,16 @@
       <c r="M194" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N194" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O194" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -12350,11 +14334,11 @@
       </c>
       <c r="I195" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J195" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999896883964539</v>
       </c>
       <c r="K195" s="7" t="inlineStr">
         <is>
@@ -12369,6 +14353,16 @@
       <c r="M195" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N195" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O195" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -12401,11 +14395,11 @@
       </c>
       <c r="I196" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J196" s="7" t="n">
-        <v>0.96</v>
+        <v>0.99974624812603</v>
       </c>
       <c r="K196" s="7" t="inlineStr">
         <is>
@@ -12420,6 +14414,16 @@
       <c r="M196" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N196" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O196" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -12452,11 +14456,11 @@
       </c>
       <c r="I197" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J197" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999016920725504</v>
       </c>
       <c r="K197" s="7" t="inlineStr">
         <is>
@@ -12471,6 +14475,16 @@
       <c r="M197" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N197" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O197" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -12503,11 +14517,11 @@
       </c>
       <c r="I198" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J198" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9997207309518542</v>
       </c>
       <c r="K198" s="7" t="inlineStr">
         <is>
@@ -12522,6 +14536,16 @@
       <c r="M198" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N198" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O198" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -12554,11 +14578,11 @@
       </c>
       <c r="I199" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J199" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999887943267822</v>
       </c>
       <c r="K199" s="7" t="inlineStr">
         <is>
@@ -12573,6 +14597,16 @@
       <c r="M199" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N199" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O199" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -12605,11 +14639,11 @@
       </c>
       <c r="I200" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J200" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999677896499634</v>
       </c>
       <c r="K200" s="7" t="inlineStr">
         <is>
@@ -12624,6 +14658,16 @@
       <c r="M200" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N200" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O200" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -12656,11 +14700,11 @@
       </c>
       <c r="I201" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J201" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9999156951904297</v>
       </c>
       <c r="K201" s="7" t="inlineStr">
         <is>
@@ -12675,6 +14719,16 @@
       <c r="M201" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N201" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O201" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -12707,11 +14761,11 @@
       </c>
       <c r="I202" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J202" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9998491108417511</v>
       </c>
       <c r="K202" s="7" t="inlineStr">
         <is>
@@ -12726,6 +14780,16 @@
       <c r="M202" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N202" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O202" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -12758,11 +14822,11 @@
       </c>
       <c r="I203" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J203" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999318718910217</v>
       </c>
       <c r="K203" s="7" t="inlineStr">
         <is>
@@ -12777,6 +14841,16 @@
       <c r="M203" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N203" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O203" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -12809,11 +14883,11 @@
       </c>
       <c r="I204" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J204" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999535083770752</v>
       </c>
       <c r="K204" s="7" t="inlineStr">
         <is>
@@ -12828,6 +14902,16 @@
       <c r="M204" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N204" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O204" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -12860,11 +14944,11 @@
       </c>
       <c r="I205" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J205" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9998824298381805</v>
       </c>
       <c r="K205" s="7" t="inlineStr">
         <is>
@@ -12879,6 +14963,16 @@
       <c r="M205" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N205" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O205" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -12911,11 +15005,11 @@
       </c>
       <c r="I206" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J206" s="7" t="n">
-        <v>0.9</v>
+        <v>0.9999567270278931</v>
       </c>
       <c r="K206" s="7" t="inlineStr">
         <is>
@@ -12930,6 +15024,16 @@
       <c r="M206" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N206" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O206" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -12962,11 +15066,11 @@
       </c>
       <c r="I207" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J207" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999897480010986</v>
       </c>
       <c r="K207" s="7" t="inlineStr">
         <is>
@@ -12981,6 +15085,16 @@
       <c r="M207" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N207" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O207" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -13013,11 +15127,11 @@
       </c>
       <c r="I208" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J208" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9996017515659332</v>
       </c>
       <c r="K208" s="7" t="inlineStr">
         <is>
@@ -13032,6 +15146,16 @@
       <c r="M208" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N208" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O208" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -13064,11 +15188,11 @@
       </c>
       <c r="I209" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J209" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9998262226581573</v>
       </c>
       <c r="K209" s="7" t="inlineStr">
         <is>
@@ -13083,6 +15207,16 @@
       <c r="M209" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N209" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O209" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -13115,11 +15249,11 @@
       </c>
       <c r="I210" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J210" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9997296120439257</v>
       </c>
       <c r="K210" s="7" t="inlineStr">
         <is>
@@ -13134,6 +15268,16 @@
       <c r="M210" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N210" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O210" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -13166,11 +15310,11 @@
       </c>
       <c r="I211" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J211" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999775886535645</v>
       </c>
       <c r="K211" s="7" t="inlineStr">
         <is>
@@ -13185,6 +15329,16 @@
       <c r="M211" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N211" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O211" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -13217,11 +15371,11 @@
       </c>
       <c r="I212" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J212" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999653339385987</v>
       </c>
       <c r="K212" s="7" t="inlineStr">
         <is>
@@ -13236,6 +15390,16 @@
       <c r="M212" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N212" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O212" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -13268,11 +15432,11 @@
       </c>
       <c r="I213" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J213" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999672889709472</v>
       </c>
       <c r="K213" s="7" t="inlineStr">
         <is>
@@ -13287,6 +15451,16 @@
       <c r="M213" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N213" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O213" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -13319,11 +15493,11 @@
       </c>
       <c r="I214" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J214" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999619424343109</v>
       </c>
       <c r="K214" s="7" t="inlineStr">
         <is>
@@ -13338,6 +15512,16 @@
       <c r="M214" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N214" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O214" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -13370,11 +15554,11 @@
       </c>
       <c r="I215" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J215" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999357759952545</v>
       </c>
       <c r="K215" s="7" t="inlineStr">
         <is>
@@ -13389,6 +15573,16 @@
       <c r="M215" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N215" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O215" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -13421,11 +15615,11 @@
       </c>
       <c r="I216" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J216" s="7" t="n">
-        <v>0.96</v>
+        <v>0.99992995262146</v>
       </c>
       <c r="K216" s="7" t="inlineStr">
         <is>
@@ -13440,6 +15634,16 @@
       <c r="M216" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N216" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O216" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -13472,11 +15676,11 @@
       </c>
       <c r="I217" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J217" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9998646676540375</v>
       </c>
       <c r="K217" s="7" t="inlineStr">
         <is>
@@ -13491,6 +15695,16 @@
       <c r="M217" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N217" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O217" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -13523,11 +15737,11 @@
       </c>
       <c r="I218" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J218" s="7" t="n">
-        <v>0.9</v>
+        <v>0.9999676942825317</v>
       </c>
       <c r="K218" s="7" t="inlineStr">
         <is>
@@ -13542,6 +15756,16 @@
       <c r="M218" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N218" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O218" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -13574,11 +15798,11 @@
       </c>
       <c r="I219" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J219" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999908089637757</v>
       </c>
       <c r="K219" s="7" t="inlineStr">
         <is>
@@ -13593,6 +15817,16 @@
       <c r="M219" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N219" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O219" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -13625,11 +15859,11 @@
       </c>
       <c r="I220" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J220" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9659256115555763</v>
       </c>
       <c r="K220" s="7" t="inlineStr">
         <is>
@@ -13644,6 +15878,16 @@
       <c r="M220" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N220" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O220" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -13676,11 +15920,11 @@
       </c>
       <c r="I221" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J221" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9999160369237264</v>
       </c>
       <c r="K221" s="7" t="inlineStr">
         <is>
@@ -13695,6 +15939,16 @@
       <c r="M221" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N221" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O221" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -13727,11 +15981,11 @@
       </c>
       <c r="I222" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J222" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9994494191237858</v>
       </c>
       <c r="K222" s="7" t="inlineStr">
         <is>
@@ -13746,6 +16000,16 @@
       <c r="M222" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N222" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O222" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -13778,11 +16042,11 @@
       </c>
       <c r="I223" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J223" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999673366546631</v>
       </c>
       <c r="K223" s="7" t="inlineStr">
         <is>
@@ -13797,6 +16061,16 @@
       <c r="M223" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N223" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O223" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -13829,11 +16103,11 @@
       </c>
       <c r="I224" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J224" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9999572277069092</v>
       </c>
       <c r="K224" s="7" t="inlineStr">
         <is>
@@ -13848,6 +16122,16 @@
       <c r="M224" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N224" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O224" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -13880,11 +16164,11 @@
       </c>
       <c r="I225" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J225" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999678134918213</v>
       </c>
       <c r="K225" s="7" t="inlineStr">
         <is>
@@ -13899,6 +16183,16 @@
       <c r="M225" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N225" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O225" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -13931,11 +16225,11 @@
       </c>
       <c r="I226" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J226" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999772906303406</v>
       </c>
       <c r="K226" s="7" t="inlineStr">
         <is>
@@ -13950,6 +16244,16 @@
       <c r="M226" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N226" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O226" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -13982,11 +16286,11 @@
       </c>
       <c r="I227" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J227" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999304115772247</v>
       </c>
       <c r="K227" s="7" t="inlineStr">
         <is>
@@ -14001,6 +16305,16 @@
       <c r="M227" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N227" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O227" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -14033,11 +16347,11 @@
       </c>
       <c r="I228" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J228" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999487638473511</v>
       </c>
       <c r="K228" s="7" t="inlineStr">
         <is>
@@ -14052,6 +16366,16 @@
       <c r="M228" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N228" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O228" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -14084,11 +16408,11 @@
       </c>
       <c r="I229" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J229" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9998885095119476</v>
       </c>
       <c r="K229" s="7" t="inlineStr">
         <is>
@@ -14103,6 +16427,16 @@
       <c r="M229" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N229" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O229" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -14135,11 +16469,11 @@
       </c>
       <c r="I230" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J230" s="7" t="n">
-        <v>0.91</v>
+        <v>0.999966636300087</v>
       </c>
       <c r="K230" s="7" t="inlineStr">
         <is>
@@ -14154,6 +16488,16 @@
       <c r="M230" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N230" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O230" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -14186,11 +16530,11 @@
       </c>
       <c r="I231" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J231" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999914407730103</v>
       </c>
       <c r="K231" s="7" t="inlineStr">
         <is>
@@ -14205,6 +16549,16 @@
       <c r="M231" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N231" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O231" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -14237,11 +16591,11 @@
       </c>
       <c r="I232" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J232" s="7" t="n">
-        <v>0.96</v>
+        <v>0.999345988035202</v>
       </c>
       <c r="K232" s="7" t="inlineStr">
         <is>
@@ -14256,6 +16610,16 @@
       <c r="M232" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N232" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O232" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -14288,11 +16652,11 @@
       </c>
       <c r="I233" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J233" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999249080816904</v>
       </c>
       <c r="K233" s="7" t="inlineStr">
         <is>
@@ -14307,6 +16671,16 @@
       <c r="M233" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N233" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O233" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -14339,11 +16713,11 @@
       </c>
       <c r="I234" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J234" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9994614124298096</v>
       </c>
       <c r="K234" s="7" t="inlineStr">
         <is>
@@ -14358,6 +16732,16 @@
       <c r="M234" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N234" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O234" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -14390,11 +16774,11 @@
       </c>
       <c r="I235" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J235" s="7" t="n">
-        <v>0.96</v>
+        <v>0.999953031539917</v>
       </c>
       <c r="K235" s="7" t="inlineStr">
         <is>
@@ -14409,6 +16793,16 @@
       <c r="M235" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N235" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O235" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -14441,11 +16835,11 @@
       </c>
       <c r="I236" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J236" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999693870544434</v>
       </c>
       <c r="K236" s="7" t="inlineStr">
         <is>
@@ -14460,6 +16854,16 @@
       <c r="M236" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N236" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O236" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -14492,11 +16896,11 @@
       </c>
       <c r="I237" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J237" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9999794721603393</v>
       </c>
       <c r="K237" s="7" t="inlineStr">
         <is>
@@ -14511,6 +16915,16 @@
       <c r="M237" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N237" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O237" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -14543,11 +16957,11 @@
       </c>
       <c r="I238" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J238" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999663233757019</v>
       </c>
       <c r="K238" s="7" t="inlineStr">
         <is>
@@ -14562,6 +16976,16 @@
       <c r="M238" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N238" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O238" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -14594,11 +17018,11 @@
       </c>
       <c r="I239" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J239" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999386370182037</v>
       </c>
       <c r="K239" s="7" t="inlineStr">
         <is>
@@ -14613,6 +17037,16 @@
       <c r="M239" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N239" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O239" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -14645,11 +17079,11 @@
       </c>
       <c r="I240" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J240" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999240398406982</v>
       </c>
       <c r="K240" s="7" t="inlineStr">
         <is>
@@ -14664,6 +17098,16 @@
       <c r="M240" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N240" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O240" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -14696,11 +17140,11 @@
       </c>
       <c r="I241" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J241" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9998617768287659</v>
       </c>
       <c r="K241" s="7" t="inlineStr">
         <is>
@@ -14715,6 +17159,16 @@
       <c r="M241" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N241" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O241" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -14747,11 +17201,11 @@
       </c>
       <c r="I242" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J242" s="7" t="n">
-        <v>0.91</v>
+        <v>0.9999620318412781</v>
       </c>
       <c r="K242" s="7" t="inlineStr">
         <is>
@@ -14766,6 +17220,16 @@
       <c r="M242" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N242" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O242" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -14798,11 +17262,11 @@
       </c>
       <c r="I243" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J243" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999854922294616</v>
       </c>
       <c r="K243" s="7" t="inlineStr">
         <is>
@@ -14817,6 +17281,16 @@
       <c r="M243" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N243" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O243" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -14849,11 +17323,11 @@
       </c>
       <c r="I244" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J244" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9997502192854881</v>
       </c>
       <c r="K244" s="7" t="inlineStr">
         <is>
@@ -14868,6 +17342,16 @@
       <c r="M244" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N244" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O244" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -14900,11 +17384,11 @@
       </c>
       <c r="I245" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J245" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999228815237681</v>
       </c>
       <c r="K245" s="7" t="inlineStr">
         <is>
@@ -14919,6 +17403,16 @@
       <c r="M245" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N245" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O245" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -14951,11 +17445,11 @@
       </c>
       <c r="I246" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J246" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9993727462632316</v>
       </c>
       <c r="K246" s="7" t="inlineStr">
         <is>
@@ -14970,6 +17464,16 @@
       <c r="M246" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N246" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O246" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -15002,11 +17506,11 @@
       </c>
       <c r="I247" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J247" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999804496765137</v>
       </c>
       <c r="K247" s="7" t="inlineStr">
         <is>
@@ -15021,6 +17525,16 @@
       <c r="M247" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N247" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O247" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -15053,11 +17567,11 @@
       </c>
       <c r="I248" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J248" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999603271484375</v>
       </c>
       <c r="K248" s="7" t="inlineStr">
         <is>
@@ -15072,6 +17586,16 @@
       <c r="M248" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N248" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O248" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -15104,11 +17628,11 @@
       </c>
       <c r="I249" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J249" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999542474746704</v>
       </c>
       <c r="K249" s="7" t="inlineStr">
         <is>
@@ -15123,6 +17647,16 @@
       <c r="M249" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N249" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O249" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -15155,11 +17689,11 @@
       </c>
       <c r="I250" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J250" s="7" t="n">
-        <v>0.96</v>
+        <v>0.999963790178299</v>
       </c>
       <c r="K250" s="7" t="inlineStr">
         <is>
@@ -15174,6 +17708,16 @@
       <c r="M250" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N250" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O250" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -15206,11 +17750,11 @@
       </c>
       <c r="I251" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J251" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9999251216650009</v>
       </c>
       <c r="K251" s="7" t="inlineStr">
         <is>
@@ -15225,6 +17769,16 @@
       <c r="M251" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N251" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O251" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -15257,11 +17811,11 @@
       </c>
       <c r="I252" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J252" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999487161636352</v>
       </c>
       <c r="K252" s="7" t="inlineStr">
         <is>
@@ -15276,6 +17830,16 @@
       <c r="M252" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N252" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O252" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -15308,11 +17872,11 @@
       </c>
       <c r="I253" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J253" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9998963326215744</v>
       </c>
       <c r="K253" s="7" t="inlineStr">
         <is>
@@ -15327,6 +17891,16 @@
       <c r="M253" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N253" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O253" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -15359,11 +17933,11 @@
       </c>
       <c r="I254" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J254" s="7" t="n">
-        <v>0.9</v>
+        <v>0.9999234899878502</v>
       </c>
       <c r="K254" s="7" t="inlineStr">
         <is>
@@ -15378,6 +17952,16 @@
       <c r="M254" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N254" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O254" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -15410,11 +17994,11 @@
       </c>
       <c r="I255" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J255" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999890327453613</v>
       </c>
       <c r="K255" s="7" t="inlineStr">
         <is>
@@ -15429,6 +18013,16 @@
       <c r="M255" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N255" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O255" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -15461,11 +18055,11 @@
       </c>
       <c r="I256" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J256" s="7" t="n">
-        <v>0.96</v>
+        <v>0.999072477221489</v>
       </c>
       <c r="K256" s="7" t="inlineStr">
         <is>
@@ -15480,6 +18074,16 @@
       <c r="M256" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N256" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O256" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -15512,11 +18116,11 @@
       </c>
       <c r="I257" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J257" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9994029005368551</v>
       </c>
       <c r="K257" s="7" t="inlineStr">
         <is>
@@ -15531,6 +18135,16 @@
       <c r="M257" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N257" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O257" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -15563,11 +18177,11 @@
       </c>
       <c r="I258" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J258" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9995468088558742</v>
       </c>
       <c r="K258" s="7" t="inlineStr">
         <is>
@@ -15582,6 +18196,16 @@
       <c r="M258" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N258" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O258" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -15614,11 +18238,11 @@
       </c>
       <c r="I259" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J259" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999943971633911</v>
       </c>
       <c r="K259" s="7" t="inlineStr">
         <is>
@@ -15633,6 +18257,16 @@
       <c r="M259" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N259" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O259" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -15665,11 +18299,11 @@
       </c>
       <c r="I260" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J260" s="7" t="n">
-        <v>0.95</v>
+        <v>0.999928605556488</v>
       </c>
       <c r="K260" s="7" t="inlineStr">
         <is>
@@ -15684,6 +18318,16 @@
       <c r="M260" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N260" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O260" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -15716,11 +18360,11 @@
       </c>
       <c r="I261" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J261" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999266068140665</v>
       </c>
       <c r="K261" s="7" t="inlineStr">
         <is>
@@ -15735,6 +18379,16 @@
       <c r="M261" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N261" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O261" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -15767,11 +18421,11 @@
       </c>
       <c r="I262" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J262" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999547362327575</v>
       </c>
       <c r="K262" s="7" t="inlineStr">
         <is>
@@ -15786,6 +18440,16 @@
       <c r="M262" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N262" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O262" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -15818,11 +18482,11 @@
       </c>
       <c r="I263" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J263" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999367892742157</v>
       </c>
       <c r="K263" s="7" t="inlineStr">
         <is>
@@ -15837,6 +18501,16 @@
       <c r="M263" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N263" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O263" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -15869,11 +18543,11 @@
       </c>
       <c r="I264" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J264" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999260425567627</v>
       </c>
       <c r="K264" s="7" t="inlineStr">
         <is>
@@ -15888,6 +18562,16 @@
       <c r="M264" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N264" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O264" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -15920,11 +18604,11 @@
       </c>
       <c r="I265" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J265" s="7" t="n">
-        <v>0.96</v>
+        <v>0.999861091375351</v>
       </c>
       <c r="K265" s="7" t="inlineStr">
         <is>
@@ -15939,6 +18623,16 @@
       <c r="M265" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N265" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O265" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -15971,11 +18665,11 @@
       </c>
       <c r="I266" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J266" s="7" t="n">
-        <v>0.91</v>
+        <v>0.9999683201313019</v>
       </c>
       <c r="K266" s="7" t="inlineStr">
         <is>
@@ -15990,6 +18684,16 @@
       <c r="M266" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N266" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O266" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -16022,11 +18726,11 @@
       </c>
       <c r="I267" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J267" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999928951263428</v>
       </c>
       <c r="K267" s="7" t="inlineStr">
         <is>
@@ -16041,6 +18745,16 @@
       <c r="M267" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N267" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O267" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -16073,11 +18787,11 @@
       </c>
       <c r="I268" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J268" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9589861482381821</v>
       </c>
       <c r="K268" s="7" t="inlineStr">
         <is>
@@ -16092,6 +18806,16 @@
       <c r="M268" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N268" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O268" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -16124,11 +18848,11 @@
       </c>
       <c r="I269" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J269" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9999013741811117</v>
       </c>
       <c r="K269" s="7" t="inlineStr">
         <is>
@@ -16143,6 +18867,16 @@
       <c r="M269" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N269" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O269" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -16175,11 +18909,11 @@
       </c>
       <c r="I270" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J270" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9997723358018058</v>
       </c>
       <c r="K270" s="7" t="inlineStr">
         <is>
@@ -16194,6 +18928,16 @@
       <c r="M270" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N270" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O270" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -16226,11 +18970,11 @@
       </c>
       <c r="I271" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J271" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999945163726807</v>
       </c>
       <c r="K271" s="7" t="inlineStr">
         <is>
@@ -16245,6 +18989,16 @@
       <c r="M271" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N271" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O271" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -16277,11 +19031,11 @@
       </c>
       <c r="I272" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J272" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999518275260926</v>
       </c>
       <c r="K272" s="7" t="inlineStr">
         <is>
@@ -16296,6 +19050,16 @@
       <c r="M272" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N272" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O272" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -16328,11 +19092,11 @@
       </c>
       <c r="I273" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J273" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999208748340607</v>
       </c>
       <c r="K273" s="7" t="inlineStr">
         <is>
@@ -16347,6 +19111,16 @@
       <c r="M273" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N273" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O273" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -16379,11 +19153,11 @@
       </c>
       <c r="I274" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J274" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999867439270019</v>
       </c>
       <c r="K274" s="7" t="inlineStr">
         <is>
@@ -16398,6 +19172,16 @@
       <c r="M274" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N274" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O274" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -16430,11 +19214,11 @@
       </c>
       <c r="I275" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J275" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999103397130966</v>
       </c>
       <c r="K275" s="7" t="inlineStr">
         <is>
@@ -16449,6 +19233,16 @@
       <c r="M275" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N275" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O275" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -16481,11 +19275,11 @@
       </c>
       <c r="I276" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J276" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999480724334717</v>
       </c>
       <c r="K276" s="7" t="inlineStr">
         <is>
@@ -16500,6 +19294,16 @@
       <c r="M276" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N276" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O276" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -16532,11 +19336,11 @@
       </c>
       <c r="I277" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J277" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999019950628281</v>
       </c>
       <c r="K277" s="7" t="inlineStr">
         <is>
@@ -16551,6 +19355,16 @@
       <c r="M277" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N277" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O277" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -16583,11 +19397,11 @@
       </c>
       <c r="I278" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J278" s="7" t="n">
-        <v>0.9</v>
+        <v>0.9999615103006363</v>
       </c>
       <c r="K278" s="7" t="inlineStr">
         <is>
@@ -16602,6 +19416,16 @@
       <c r="M278" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N278" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O278" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -16634,11 +19458,11 @@
       </c>
       <c r="I279" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J279" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999904990196228</v>
       </c>
       <c r="K279" s="7" t="inlineStr">
         <is>
@@ -16653,6 +19477,16 @@
       <c r="M279" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N279" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O279" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -16685,11 +19519,11 @@
       </c>
       <c r="I280" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J280" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9985221773386002</v>
       </c>
       <c r="K280" s="7" t="inlineStr">
         <is>
@@ -16704,6 +19538,16 @@
       <c r="M280" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N280" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O280" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -16736,11 +19580,11 @@
       </c>
       <c r="I281" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J281" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9998856981595358</v>
       </c>
       <c r="K281" s="7" t="inlineStr">
         <is>
@@ -16755,6 +19599,16 @@
       <c r="M281" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N281" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O281" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -16787,11 +19641,11 @@
       </c>
       <c r="I282" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J282" s="7" t="n">
-        <v>0.95</v>
+        <v>0.999435910156795</v>
       </c>
       <c r="K282" s="7" t="inlineStr">
         <is>
@@ -16806,6 +19660,16 @@
       <c r="M282" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N282" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O282" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -16838,11 +19702,11 @@
       </c>
       <c r="I283" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J283" s="7" t="n">
-        <v>0.96</v>
+        <v>0.99998939037323</v>
       </c>
       <c r="K283" s="7" t="inlineStr">
         <is>
@@ -16857,6 +19721,16 @@
       <c r="M283" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N283" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O283" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -16889,11 +19763,11 @@
       </c>
       <c r="I284" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J284" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9999685525894165</v>
       </c>
       <c r="K284" s="7" t="inlineStr">
         <is>
@@ -16908,6 +19782,16 @@
       <c r="M284" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N284" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O284" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -16940,11 +19824,11 @@
       </c>
       <c r="I285" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J285" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999571800231933</v>
       </c>
       <c r="K285" s="7" t="inlineStr">
         <is>
@@ -16959,6 +19843,16 @@
       <c r="M285" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N285" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O285" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -16991,11 +19885,11 @@
       </c>
       <c r="I286" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J286" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9998994469642639</v>
       </c>
       <c r="K286" s="7" t="inlineStr">
         <is>
@@ -17010,6 +19904,16 @@
       <c r="M286" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N286" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O286" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -17042,11 +19946,11 @@
       </c>
       <c r="I287" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J287" s="7" t="n">
-        <v>0.96</v>
+        <v>0.999941349029541</v>
       </c>
       <c r="K287" s="7" t="inlineStr">
         <is>
@@ -17061,6 +19965,16 @@
       <c r="M287" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N287" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O287" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -17093,11 +20007,11 @@
       </c>
       <c r="I288" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J288" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999351263046264</v>
       </c>
       <c r="K288" s="7" t="inlineStr">
         <is>
@@ -17112,6 +20026,16 @@
       <c r="M288" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N288" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O288" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -17144,11 +20068,11 @@
       </c>
       <c r="I289" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J289" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9998669922351837</v>
       </c>
       <c r="K289" s="7" t="inlineStr">
         <is>
@@ -17163,6 +20087,16 @@
       <c r="M289" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N289" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O289" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -17195,11 +20129,11 @@
       </c>
       <c r="I290" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J290" s="7" t="n">
-        <v>0.92</v>
+        <v>0.9999515116214752</v>
       </c>
       <c r="K290" s="7" t="inlineStr">
         <is>
@@ -17214,6 +20148,16 @@
       <c r="M290" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N290" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O290" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -17246,11 +20190,11 @@
       </c>
       <c r="I291" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J291" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999853491783142</v>
       </c>
       <c r="K291" s="7" t="inlineStr">
         <is>
@@ -17265,6 +20209,16 @@
       <c r="M291" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N291" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O291" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -17297,11 +20251,11 @@
       </c>
       <c r="I292" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J292" s="7" t="n">
-        <v>0.93</v>
+        <v>0.9996262043714523</v>
       </c>
       <c r="K292" s="7" t="inlineStr">
         <is>
@@ -17316,6 +20270,16 @@
       <c r="M292" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N292" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O292" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -17348,11 +20312,11 @@
       </c>
       <c r="I293" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J293" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9997453987598419</v>
       </c>
       <c r="K293" s="7" t="inlineStr">
         <is>
@@ -17367,6 +20331,16 @@
       <c r="M293" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N293" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O293" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -17399,11 +20373,11 @@
       </c>
       <c r="I294" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J294" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9662841320037842</v>
       </c>
       <c r="K294" s="7" t="inlineStr">
         <is>
@@ -17418,6 +20392,16 @@
       <c r="M294" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N294" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O294" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -17450,11 +20434,11 @@
       </c>
       <c r="I295" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J295" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999749660491943</v>
       </c>
       <c r="K295" s="7" t="inlineStr">
         <is>
@@ -17469,6 +20453,16 @@
       <c r="M295" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N295" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O295" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -17501,11 +20495,11 @@
       </c>
       <c r="I296" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J296" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9996129274368286</v>
       </c>
       <c r="K296" s="7" t="inlineStr">
         <is>
@@ -17520,6 +20514,16 @@
       <c r="M296" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N296" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O296" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -17552,11 +20556,11 @@
       </c>
       <c r="I297" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J297" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9999366879463196</v>
       </c>
       <c r="K297" s="7" t="inlineStr">
         <is>
@@ -17571,6 +20575,16 @@
       <c r="M297" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N297" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O297" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -17603,11 +20617,11 @@
       </c>
       <c r="I298" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J298" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9998530894517899</v>
       </c>
       <c r="K298" s="7" t="inlineStr">
         <is>
@@ -17622,6 +20636,16 @@
       <c r="M298" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N298" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O298" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -17654,11 +20678,11 @@
       </c>
       <c r="I299" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J299" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9998990148305893</v>
       </c>
       <c r="K299" s="7" t="inlineStr">
         <is>
@@ -17673,6 +20697,16 @@
       <c r="M299" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N299" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O299" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -17705,11 +20739,11 @@
       </c>
       <c r="I300" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J300" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999520540237427</v>
       </c>
       <c r="K300" s="7" t="inlineStr">
         <is>
@@ -17724,6 +20758,16 @@
       <c r="M300" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N300" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O300" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -17756,11 +20800,11 @@
       </c>
       <c r="I301" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J301" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9999033659696579</v>
       </c>
       <c r="K301" s="7" t="inlineStr">
         <is>
@@ -17775,6 +20819,16 @@
       <c r="M301" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N301" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O301" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -17807,11 +20861,11 @@
       </c>
       <c r="I302" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J302" s="7" t="n">
-        <v>0.9</v>
+        <v>0.9999552816152573</v>
       </c>
       <c r="K302" s="7" t="inlineStr">
         <is>
@@ -17826,6 +20880,16 @@
       <c r="M302" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N302" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O302" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -17858,11 +20922,11 @@
       </c>
       <c r="I303" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J303" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9999863624572753</v>
       </c>
       <c r="K303" s="7" t="inlineStr">
         <is>
@@ -17877,6 +20941,16 @@
       <c r="M303" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N303" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O303" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -17909,11 +20983,11 @@
       </c>
       <c r="I304" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J304" s="7" t="n">
-        <v>0.95</v>
+        <v>0.998554952442646</v>
       </c>
       <c r="K304" s="7" t="inlineStr">
         <is>
@@ -17928,6 +21002,16 @@
       <c r="M304" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N304" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O304" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -17960,11 +21044,11 @@
       </c>
       <c r="I305" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J305" s="7" t="n">
-        <v>0.96</v>
+        <v>0.999879002571106</v>
       </c>
       <c r="K305" s="7" t="inlineStr">
         <is>
@@ -17979,6 +21063,16 @@
       <c r="M305" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N305" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O305" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -18011,11 +21105,11 @@
       </c>
       <c r="I306" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J306" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9997740745544433</v>
       </c>
       <c r="K306" s="7" t="inlineStr">
         <is>
@@ -18030,6 +21124,16 @@
       <c r="M306" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N306" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O306" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -18062,11 +21166,11 @@
       </c>
       <c r="I307" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J307" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999620914459229</v>
       </c>
       <c r="K307" s="7" t="inlineStr">
         <is>
@@ -18081,6 +21185,16 @@
       <c r="M307" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N307" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O307" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -18113,11 +21227,11 @@
       </c>
       <c r="I308" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J308" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999487519264221</v>
       </c>
       <c r="K308" s="7" t="inlineStr">
         <is>
@@ -18132,6 +21246,16 @@
       <c r="M308" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N308" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O308" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -18164,11 +21288,11 @@
       </c>
       <c r="I309" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J309" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999499320983887</v>
       </c>
       <c r="K309" s="7" t="inlineStr">
         <is>
@@ -18183,6 +21307,16 @@
       <c r="M309" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N309" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O309" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -18215,11 +21349,11 @@
       </c>
       <c r="I310" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J310" s="7" t="n">
-        <v>0.96</v>
+        <v>0.999956339597702</v>
       </c>
       <c r="K310" s="7" t="inlineStr">
         <is>
@@ -18234,6 +21368,16 @@
       <c r="M310" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N310" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O310" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -18266,11 +21410,11 @@
       </c>
       <c r="I311" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J311" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999371767044067</v>
       </c>
       <c r="K311" s="7" t="inlineStr">
         <is>
@@ -18285,6 +21429,16 @@
       <c r="M311" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N311" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O311" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -18317,11 +21471,11 @@
       </c>
       <c r="I312" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J312" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9999411582946778</v>
       </c>
       <c r="K312" s="7" t="inlineStr">
         <is>
@@ -18336,6 +21490,16 @@
       <c r="M312" s="7" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N312" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O312" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -18368,11 +21532,11 @@
       </c>
       <c r="I313" s="7" t="inlineStr">
         <is>
-          <t>ocr-tesseract</t>
+          <t>ocr-rapidocr</t>
         </is>
       </c>
       <c r="J313" s="7" t="n">
-        <v>0.96</v>
+        <v>0.9998748600482941</v>
       </c>
       <c r="K313" s="7" t="inlineStr">
         <is>
@@ -18389,9 +21553,19 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N313" s="7" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O313" s="7" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M313"/>
+  <autoFilter ref="A1:O313"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18402,10 +21576,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
     <col width="65" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -18441,7 +21615,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>33b0712165514ce4428b278ec50d59671af69fa529c0a77d2139f7967ab01cab</t>
+          <t>ae340164215b16ee606a868677b2c0f8131e977a11c9626475fa3e2264eeb856</t>
         </is>
       </c>
     </row>
@@ -18480,65 +21654,117 @@
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>cells</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>288</v>
+          <t>Export type</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Draft Excel</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>cells with source boxes</t>
+          <t>Non-empty exported cells</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>288</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>equations</t>
+          <t>Cells with source boxes</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>equation checks</t>
+          <t>Cells requiring full-page evidence review</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>failed equation checks</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>0</v>
+          <t>Cell source-box coverage</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
+          <t>cells</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>cells with source boxes</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>equations</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>equation checks</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>failed equation checks</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
           <t>proposals with multiple equations</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B17" s="7" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B12"/>
+  <autoFilter ref="A1:B17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
